--- a/kurs-na-zachet.xlsx
+++ b/kurs-na-zachet.xlsx
@@ -1519,7 +1519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1693,6 +1693,18 @@
       <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Ячейки с жёлтым фоном — твои данные. Остальное считается формулами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Связь со страницей</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>В файле kurs-na-zachet.html кнопка «Загрузить из Excel» читает листы «Дневник», «План» (колонка «Сделано») и «Расчёт» из этого файла. Кнопка «Сохранить в Excel» создаёт отдельный файл с таким же листом «Дневник».</t>
         </is>
       </c>
     </row>
